--- a/booking_forms/049_dog_boarding_booking_form--booking_forms.xlsx
+++ b/booking_forms/049_dog_boarding_booking_form--booking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -849,8 +849,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -878,12 +878,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'monday'}</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Monday'}</t>
+          <t>Monday</t>
         </is>
       </c>
     </row>
@@ -895,12 +895,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'tuesday'}</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Tuesday'}</t>
+          <t>Tuesday</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'wednesday'}</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Wednesday'}</t>
+          <t>Wednesday</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'thursday'}</t>
+          <t>thursday</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Thursday'}</t>
+          <t>Thursday</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'friday'}</t>
+          <t>friday</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Friday'}</t>
+          <t>Friday</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'walking'}</t>
+          <t>walking</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Walking'}</t>
+          <t>Walking</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'feeding'}</t>
+          <t>feeding</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Feeding'}</t>
+          <t>Feeding</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'bathing'}</t>
+          <t>bathing</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Bathing'}</t>
+          <t>Bathing</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'training'}</t>
+          <t>training</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Training'}</t>
+          <t>Training</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'cash'}</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Cash'}</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
@@ -1048,12 +1048,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'card'}</t>
+          <t>card</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Card'}</t>
+          <t>Card</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'paypal'}</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'PayPal'}</t>
+          <t>PayPal</t>
         </is>
       </c>
     </row>
